--- a/Extra/tasks/Phân Công_Tuần 1,2.xlsx
+++ b/Extra/tasks/Phân Công_Tuần 1,2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTH mãi đỉnh\Lập trình Mạng\Project\NET_09-CO-TUONG\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTH mãi đỉnh\Lập trình Mạng\Project\NET_09-CO-TUONG\Extra\tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36699DE-FD9E-4F4C-9137-71D8201434C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61041BC7-D37C-4E6D-A744-76B7CD17145B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,12 +61,6 @@
     <t>Protocol.cs, GameTimer.cs</t>
   </si>
   <si>
-    <t>1. Soạn file Word báo cáo: Mục tiêu, lý do chọn đề tài, danh sách thành viên.2. Quản lý tiến độ (nhắc nhở mọi người commit đúng hạn).3. Chuẩn bị kịch bản Test kết nối tuần 1 (các lỗi có thể gặp).</t>
-  </si>
-  <si>
-    <t>Bao_cao.docx, Task_List.xlsx</t>
-  </si>
-  <si>
     <t>Trần Nhật Sinh</t>
   </si>
   <si>
@@ -85,7 +79,13 @@
     <t>Ngô Quốc An</t>
   </si>
   <si>
-    <t>FormMain.cs &amp; Folder Assets</t>
+    <t>1. Soạn file Word báo cáo: Mục tiêu, lý do chọn đề tài, danh sách thành viên.2. Quản lý tiến độ (nhắc nhở mọi người commit đúng hạn).3. Giao diện khung trò chuyện (chat)</t>
+  </si>
+  <si>
+    <t>Bao_cao.docx, ChatBox.cs</t>
+  </si>
+  <si>
+    <t>FormMain.cs &amp; Folder Images</t>
   </si>
 </sst>
 </file>
@@ -414,7 +414,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -428,7 +428,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
@@ -442,7 +442,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
@@ -456,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
@@ -470,7 +470,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
@@ -484,13 +484,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Extra/tasks/Phân Công_Tuần 1,2.xlsx
+++ b/Extra/tasks/Phân Công_Tuần 1,2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTH mãi đỉnh\Lập trình Mạng\Project\NET_09-CO-TUONG\Extra\tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61041BC7-D37C-4E6D-A744-76B7CD17145B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE941ED-AAAF-49EE-9253-77BF2EDB5651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,9 +34,6 @@
     <t>Sản phẩm bàn giao</t>
   </si>
   <si>
-    <t>1. Tạo Solution C# chuẩn trên Visual Studio.2. Viết code mở cổng TcpListener (File ServerManager.cs).3. Thiết lập hệ thống ghi nhật ký (File Logger.cs).4. Xử lý đa luồng để nhận nhiều Client (File ClientHandler.cs).</t>
-  </si>
-  <si>
     <t>Link GitHub &amp; Project Server chạy được</t>
   </si>
   <si>
@@ -86,6 +83,9 @@
   </si>
   <si>
     <t>FormMain.cs &amp; Folder Images</t>
+  </si>
+  <si>
+    <t>1. Tạo Solution C# chuẩn trên Visual Studio.2. Viết code mở cổng TcpListener (File ServerManager.cs).3. Thiết lập hệ thống ghi nhật ký (File Logger.cs).</t>
   </si>
 </sst>
 </file>
@@ -414,13 +414,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -428,13 +428,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -442,13 +442,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -456,13 +456,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -470,13 +470,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -484,13 +484,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
